--- a/salidas/empresas/CHTR.xlsx
+++ b/salidas/empresas/CHTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B18" t="n">
@@ -811,7 +823,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B19" t="n">
@@ -836,7 +848,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B20" t="n">
@@ -861,7 +873,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B21" t="n">
@@ -886,7 +898,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B22" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B23" t="n">
@@ -936,7 +948,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B24" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B25" t="n">
@@ -986,7 +998,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B26" t="n">
@@ -1011,7 +1023,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B27" t="n">
@@ -1036,7 +1048,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B28" t="n">
@@ -1061,7 +1073,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B29" t="n">
@@ -1086,7 +1098,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B30" t="n">
@@ -1111,7 +1123,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B31" t="n">
@@ -1136,7 +1148,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B32" t="n">
@@ -1161,7 +1173,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B33" t="n">
@@ -1186,7 +1198,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B34" t="n">
@@ -1211,7 +1223,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B35" t="n">
@@ -1236,7 +1248,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B36" t="n">
@@ -1261,7 +1273,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B37" t="n">
@@ -1286,7 +1298,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B38" t="n">
@@ -1311,7 +1323,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B39" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B40" t="n">
@@ -1365,7 +1377,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B41" t="n">
@@ -1392,7 +1404,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B42" t="n">
@@ -1419,7 +1431,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B43" t="n">
@@ -1446,7 +1458,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B44" t="n">
@@ -1473,7 +1485,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B45" t="n">
@@ -1500,7 +1512,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B46" t="n">
@@ -1527,7 +1539,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B47" t="n">
@@ -1554,7 +1566,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B48" t="n">
@@ -1581,7 +1593,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B49" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B50" t="n">
@@ -1635,7 +1647,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B51" t="n">
@@ -1662,7 +1674,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B52" t="n">
@@ -1689,7 +1701,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B53" t="n">
@@ -1716,7 +1728,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B54" t="n">
@@ -1743,7 +1755,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B55" t="n">
@@ -1770,7 +1782,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B56" t="n">
@@ -1797,7 +1809,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B57" t="n">
@@ -1824,7 +1836,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B58" t="n">
@@ -1851,7 +1863,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B59" t="n">
@@ -1878,7 +1890,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B60" t="n">
@@ -1905,7 +1917,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B61" t="n">
@@ -1932,7 +1944,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B62" t="n">
@@ -1959,7 +1971,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B63" t="n">
@@ -1986,7 +1998,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B64" t="n">
@@ -2013,7 +2025,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B65" t="n">
@@ -2040,7 +2052,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B66" t="n">
@@ -2067,7 +2079,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B67" t="n">
@@ -2094,7 +2106,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B68" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B69" t="n">
@@ -2148,7 +2160,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B70" t="n">
@@ -2175,7 +2187,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B71" t="n">
@@ -2200,7 +2212,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B72" t="n">
@@ -2225,7 +2237,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B73" t="n">
@@ -2250,7 +2262,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B74" t="n">
@@ -2275,7 +2287,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B75" t="n">
@@ -2302,7 +2314,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B76" t="n">
@@ -2329,7 +2341,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B77" t="n">
@@ -2356,7 +2368,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B78" t="n">
@@ -2383,7 +2395,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B79" t="n">
@@ -2410,7 +2422,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B80" t="n">
@@ -2437,7 +2449,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B81" t="n">
@@ -2464,7 +2476,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B82" t="n">
@@ -2489,7 +2501,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B83" t="n">
@@ -2514,7 +2526,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B84" t="n">
@@ -2539,7 +2551,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B85" t="n">
@@ -2564,7 +2576,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B86" t="n">
@@ -2589,7 +2601,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B87" t="n">
@@ -2618,7 +2630,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B88" t="n">
@@ -2647,7 +2659,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B89" t="n">
@@ -2676,7 +2688,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B90" t="n">
@@ -2705,7 +2717,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B91" t="n">
@@ -2734,7 +2746,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B92" t="n">
@@ -2763,7 +2775,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B93" t="n">
@@ -2792,7 +2804,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B94" t="n">
@@ -2821,7 +2833,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B95" t="n">
@@ -2850,7 +2862,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B96" t="n">
@@ -2879,7 +2891,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B97" t="n">
@@ -2908,7 +2920,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B98" t="n">
@@ -2937,7 +2949,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B99" t="n">
@@ -2966,7 +2978,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B100" t="n">
@@ -2995,7 +3007,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B101" t="n">
@@ -3024,7 +3036,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B102" t="n">
@@ -3053,7 +3065,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B103" t="n">
@@ -3082,7 +3094,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B104" t="n">
@@ -3111,7 +3123,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B105" t="n">
@@ -3140,7 +3152,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B106" t="n">
@@ -3169,7 +3181,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B107" t="n">
@@ -3198,7 +3210,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B108" t="n">
@@ -3227,7 +3239,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B109" t="n">
@@ -3256,7 +3268,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B110" t="n">
@@ -3285,7 +3297,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B111" t="n">
@@ -3314,7 +3326,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B112" t="n">
@@ -3343,7 +3355,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B113" t="n">
@@ -3372,7 +3384,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B114" t="n">
@@ -3401,7 +3413,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B115" t="n">
@@ -3430,7 +3442,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B116" t="n">
@@ -3459,7 +3471,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B117" t="n">
@@ -3488,7 +3500,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B118" t="n">
@@ -3517,7 +3529,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B119" t="n">
@@ -3546,7 +3558,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B120" t="n">
@@ -3575,7 +3587,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B121" t="n">
@@ -3604,7 +3616,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B122" t="n">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B123" t="n">
@@ -3662,7 +3674,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B124" t="n">
@@ -3691,7 +3703,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B125" t="n">
@@ -3720,7 +3732,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B126" t="n">
@@ -3749,7 +3761,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B127" t="n">
@@ -3778,7 +3790,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B128" t="n">
@@ -3807,7 +3819,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B129" t="n">
@@ -3836,7 +3848,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B130" t="n">
@@ -3865,7 +3877,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B131" t="n">
@@ -3894,7 +3906,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B132" t="n">
@@ -3923,7 +3935,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B133" t="n">
@@ -3952,7 +3964,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B134" t="n">
@@ -3981,7 +3993,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B135" t="n">
@@ -4010,7 +4022,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B136" t="n">
@@ -4039,7 +4051,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B137" t="n">
@@ -4068,7 +4080,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B138" t="n">
@@ -4097,7 +4109,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B139" t="n">
@@ -4126,7 +4138,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B140" t="n">
@@ -4155,7 +4167,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B141" t="n">
@@ -4184,7 +4196,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B142" t="n">
@@ -4213,7 +4225,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B143" t="n">
@@ -4242,7 +4254,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B144" t="n">
@@ -4271,7 +4283,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B145" t="n">
@@ -4300,7 +4312,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B146" t="n">
@@ -4329,7 +4341,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B147" t="n">
@@ -4358,7 +4370,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B148" t="n">
@@ -4387,7 +4399,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B149" t="n">
@@ -4416,7 +4428,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B150" t="n">
@@ -4445,7 +4457,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B151" t="n">
@@ -4474,7 +4486,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B152" t="n">
@@ -4503,7 +4515,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B153" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B154" t="n">
@@ -4561,7 +4573,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B155" t="n">
@@ -4590,7 +4602,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B156" t="n">
@@ -4619,7 +4631,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B157" t="n">
@@ -4648,7 +4660,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B158" t="n">
@@ -4677,7 +4689,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B159" t="n">
@@ -4706,7 +4718,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B160" t="n">
@@ -4735,7 +4747,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B161" t="n">
@@ -4764,7 +4776,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B162" t="n">
@@ -4793,7 +4805,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B163" t="n">
@@ -4822,7 +4834,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B164" t="n">
@@ -4851,7 +4863,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B165" t="n">
@@ -4880,7 +4892,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B166" t="n">
@@ -4909,7 +4921,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B167" t="n">
@@ -4938,7 +4950,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B168" t="n">
@@ -4967,7 +4979,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B169" t="n">
@@ -4996,7 +5008,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B170" t="n">
@@ -5025,7 +5037,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B171" t="n">
@@ -5054,7 +5066,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B172" t="n">
@@ -5083,7 +5095,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B173" t="n">
@@ -5112,7 +5124,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B174" t="n">
@@ -5141,7 +5153,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B175" t="n">
@@ -5170,7 +5182,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B176" t="n">
@@ -5199,7 +5211,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B177" t="n">
@@ -5228,7 +5240,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B178" t="n">
@@ -5257,7 +5269,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B179" t="n">
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B180" t="n">
@@ -5315,7 +5327,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B181" t="n">
@@ -5344,7 +5356,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B182" t="n">
@@ -5373,7 +5385,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B183" t="n">
@@ -5402,7 +5414,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B184" t="n">
@@ -5431,7 +5443,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B185" t="n">
@@ -5460,7 +5472,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B186" t="n">
@@ -5489,7 +5501,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B187" t="n">
@@ -5518,7 +5530,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B188" t="n">
@@ -5547,7 +5559,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B189" t="n">
@@ -5576,7 +5588,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B190" t="n">
@@ -5605,7 +5617,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B191" t="n">
@@ -5634,7 +5646,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B192" t="n">
@@ -5663,7 +5675,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B193" t="n">
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B194" t="n">
@@ -5721,7 +5733,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B195" t="n">
@@ -5750,7 +5762,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B196" t="n">
@@ -5779,7 +5791,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B197" t="n">
@@ -5808,7 +5820,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B198" t="n">
@@ -5837,7 +5849,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B199" t="n">
@@ -5866,7 +5878,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B200" t="n">
@@ -5895,7 +5907,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B201" t="n">
@@ -5924,32 +5936,32 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B202" t="n">
-        <v>116.6100006103516</v>
+        <v>117.5500030517578</v>
       </c>
       <c r="C202" t="n">
-        <v>116.6100006103516</v>
+        <v>117.5500030517578</v>
       </c>
       <c r="D202" t="n">
-        <v>49830800</v>
+        <v>53452100</v>
       </c>
       <c r="E202" t="n">
         <v>38.44</v>
       </c>
       <c r="F202" t="n">
-        <v>3.03355880880207</v>
+        <v>3.058012566382878</v>
       </c>
       <c r="G202" t="n">
         <v>120121017</v>
       </c>
       <c r="H202" t="n">
-        <v>14007311865.68605</v>
+        <v>14120225914.93025</v>
       </c>
       <c r="I202" t="n">
-        <v>0.414838312599368</v>
+        <v>0.4449854100053116</v>
       </c>
     </row>
   </sheetData>
@@ -5981,75 +5993,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -6085,13 +6097,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -6127,13 +6139,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -6169,13 +6181,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -6202,7 +6214,7 @@
       <c r="I5" t="n">
         <v>-2.09</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K5" t="n">
@@ -6215,13 +6227,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -6248,7 +6260,7 @@
       <c r="I6" t="n">
         <v>-3.27</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K6" t="n">
@@ -6261,13 +6273,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -6294,7 +6306,7 @@
       <c r="I7" t="n">
         <v>-3.53</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K7" t="n">
@@ -6307,13 +6319,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -6340,7 +6352,7 @@
       <c r="I8" t="n">
         <v>-3.48</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K8" t="n">
@@ -6353,13 +6365,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -6386,7 +6398,7 @@
       <c r="I9" t="n">
         <v>-3.37</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K9" t="n">
@@ -6399,13 +6411,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -6432,7 +6444,7 @@
       <c r="I10" t="n">
         <v>-3.35</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K10" t="n">
@@ -6445,13 +6457,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -6478,7 +6490,7 @@
       <c r="I11" t="n">
         <v>-3.21</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K11" t="n">
@@ -6491,13 +6503,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -6524,7 +6536,7 @@
       <c r="I12" t="n">
         <v>-3.29</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K12" t="n">
@@ -6537,13 +6549,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -6570,7 +6582,7 @@
       <c r="I13" t="n">
         <v>-3.07</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K13" t="n">
@@ -6583,13 +6595,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6616,7 +6628,7 @@
       <c r="I14" t="n">
         <v>-2.54</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K14" t="n">
@@ -6629,13 +6641,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6662,7 +6674,7 @@
       <c r="I15" t="n">
         <v>-2.66</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K15" t="n">
@@ -6675,13 +6687,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6708,7 +6720,7 @@
       <c r="I16" t="n">
         <v>-2.47</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K16" t="n">
@@ -6721,13 +6733,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6754,7 +6766,7 @@
       <c r="I17" t="n">
         <v>-1.71</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K17" t="n">
@@ -6767,13 +6779,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6800,7 +6812,7 @@
       <c r="I18" t="n">
         <v>-1.64</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="K18" t="n">
@@ -6813,13 +6825,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6846,7 +6858,7 @@
       <c r="I19" t="n">
         <v>-1.1</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="K19" t="n">
@@ -6859,13 +6871,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6892,7 +6904,7 @@
       <c r="I20" t="n">
         <v>-0.9099999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="K20" t="n">
@@ -6905,13 +6917,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6938,7 +6950,7 @@
       <c r="I21" t="n">
         <v>-1.7</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K21" t="n">
@@ -6951,13 +6963,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6984,7 +6996,7 @@
       <c r="I22" t="n">
         <v>-2.08</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K22" t="n">
@@ -6997,13 +7009,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -7030,7 +7042,7 @@
       <c r="I23" t="n">
         <v>-2.75</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K23" t="n">
@@ -7043,13 +7055,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -7076,7 +7088,7 @@
       <c r="I24" t="n">
         <v>-1.78</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K24" t="n">
@@ -7089,13 +7101,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -7122,7 +7134,7 @@
       <c r="I25" t="n">
         <v>-2.43</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="K25" t="n">
@@ -7135,13 +7147,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -7168,7 +7180,7 @@
       <c r="I26" t="n">
         <v>-3.56</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K26" t="n">
@@ -7181,13 +7193,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -7214,7 +7226,7 @@
       <c r="I27" t="n">
         <v>12.7</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K27" t="n">
@@ -7227,13 +7239,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -7260,7 +7272,7 @@
       <c r="I28" t="n">
         <v>12.91</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K28" t="n">
@@ -7273,13 +7285,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -7306,7 +7318,7 @@
       <c r="I29" t="n">
         <v>15.67</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K29" t="n">
@@ -7319,13 +7331,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -7352,7 +7364,7 @@
       <c r="I30" t="n">
         <v>18.1</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K30" t="n">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -7398,7 +7410,7 @@
       <c r="I31" t="n">
         <v>3.45</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K31" t="n">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -7444,7 +7456,7 @@
       <c r="I32" t="n">
         <v>2.95</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K32" t="n">
@@ -7457,13 +7469,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -7490,7 +7502,7 @@
       <c r="I33" t="n">
         <v>35.84</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="K33" t="n">
@@ -7503,13 +7515,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -7536,7 +7548,7 @@
       <c r="I34" t="n">
         <v>35.97000000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K34" t="n">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7582,7 +7594,7 @@
       <c r="I35" t="n">
         <v>36.6</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K35" t="n">
@@ -7595,13 +7607,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7628,7 +7640,7 @@
       <c r="I36" t="n">
         <v>38.52</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K36" t="n">
@@ -7641,13 +7653,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7674,7 +7686,7 @@
       <c r="I37" t="n">
         <v>5.25</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="K37" t="n">
@@ -7687,13 +7699,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7720,7 +7732,7 @@
       <c r="I38" t="n">
         <v>5.66</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="K38" t="n">
@@ -7733,13 +7745,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7766,7 +7778,7 @@
       <c r="I39" t="n">
         <v>5.9</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K39" t="n">
@@ -7779,13 +7791,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7812,7 +7824,7 @@
       <c r="I40" t="n">
         <v>5.53</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K40" t="n">
@@ -7825,13 +7837,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7858,7 +7870,7 @@
       <c r="I41" t="n">
         <v>7.52</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="K41" t="n">
@@ -7871,13 +7883,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7904,7 +7916,7 @@
       <c r="I42" t="n">
         <v>8.27</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K42" t="n">
@@ -7917,13 +7929,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7950,7 +7962,7 @@
       <c r="I43" t="n">
         <v>10.51</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K43" t="n">
@@ -7963,13 +7975,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7996,7 +8008,7 @@
       <c r="I44" t="n">
         <v>12.67</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K44" t="n">
@@ -8009,13 +8021,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -8042,7 +8054,7 @@
       <c r="I45" t="n">
         <v>15.44</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="K45" t="n">
@@ -8055,13 +8067,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -8088,7 +8100,7 @@
       <c r="I46" t="n">
         <v>17.69</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K46" t="n">
@@ -8101,13 +8113,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -8134,7 +8146,7 @@
       <c r="I47" t="n">
         <v>19.35</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K47" t="n">
@@ -8147,13 +8159,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -8180,7 +8192,7 @@
       <c r="I48" t="n">
         <v>21.95</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K48" t="n">
@@ -8193,13 +8205,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -8226,7 +8238,7 @@
       <c r="I49" t="n">
         <v>24.47</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="K49" t="n">
@@ -8239,13 +8251,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -8272,7 +8284,7 @@
       <c r="I50" t="n">
         <v>27.26</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K50" t="n">
@@ -8285,13 +8297,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -8318,7 +8330,7 @@
       <c r="I51" t="n">
         <v>30.77</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K51" t="n">
@@ -8331,13 +8343,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -8364,7 +8376,7 @@
       <c r="I52" t="n">
         <v>31.65</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K52" t="n">
@@ -8377,13 +8389,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -8410,7 +8422,7 @@
       <c r="I53" t="n">
         <v>30.74</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="K53" t="n">
@@ -8423,13 +8435,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -8456,7 +8468,7 @@
       <c r="I54" t="n">
         <v>30.48999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="K54" t="n">
@@ -8469,13 +8481,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -8502,7 +8514,7 @@
       <c r="I55" t="n">
         <v>29.74</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="K55" t="n">
@@ -8515,13 +8527,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -8548,7 +8560,7 @@
       <c r="I56" t="n">
         <v>30.61</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="K56" t="n">
@@ -8561,13 +8573,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -8594,7 +8606,7 @@
       <c r="I57" t="n">
         <v>29.98999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="K57" t="n">
@@ -8607,13 +8619,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -8640,7 +8652,7 @@
       <c r="I58" t="n">
         <v>30.89</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="K58" t="n">
@@ -8653,13 +8665,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -8686,7 +8698,7 @@
       <c r="I59" t="n">
         <v>31.32999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="K59" t="n">
@@ -8699,13 +8711,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -8732,7 +8744,7 @@
       <c r="I60" t="n">
         <v>31.9</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K60" t="n">
@@ -8745,13 +8757,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -8778,7 +8790,7 @@
       <c r="I61" t="n">
         <v>34.97</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K61" t="n">
@@ -8791,13 +8803,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -8824,7 +8836,7 @@
       <c r="I62" t="n">
         <v>35.84</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="K62" t="n">
@@ -8837,13 +8849,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -8870,7 +8882,7 @@
       <c r="I63" t="n">
         <v>36.53</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="K63" t="n">
@@ -8883,13 +8895,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -8916,7 +8928,7 @@
       <c r="I64" t="n">
         <v>36.05</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K64" t="n">
@@ -8929,13 +8941,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -8962,7 +8974,7 @@
       <c r="I65" t="n">
         <v>36.21</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K65" t="n">
@@ -8975,13 +8987,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -9008,7 +9020,7 @@
       <c r="I66" t="n">
         <v>36.95999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="K66" t="n">
@@ -9021,13 +9033,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -9054,7 +9066,7 @@
       <c r="I67" t="n">
         <v>38.44</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="K67" t="n">
@@ -9092,57 +9104,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C2" t="n">
@@ -9176,10 +9188,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C3" t="n">
@@ -9213,10 +9225,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C4" t="n">
@@ -9246,10 +9258,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C5" t="n">
@@ -9279,10 +9291,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41037</v>
       </c>
       <c r="C6" t="n">
@@ -9312,10 +9324,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C7" t="n">
@@ -9345,10 +9357,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C8" t="n">
@@ -9378,10 +9390,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C9" t="n">
@@ -9411,10 +9423,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C10" t="n">
@@ -9444,10 +9456,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C11" t="n">
@@ -9477,10 +9489,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C12" t="n">
@@ -9514,10 +9526,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="C13" t="n">
@@ -9547,10 +9559,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="C14" t="n">
@@ -9580,10 +9592,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C15" t="n">
@@ -9613,10 +9625,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C16" t="n">
@@ -9646,10 +9658,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C17" t="n">
@@ -9683,10 +9695,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C18" t="n">
@@ -9720,10 +9732,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C19" t="n">
@@ -9757,10 +9769,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42410</v>
       </c>
       <c r="C20" t="n">
@@ -9794,10 +9806,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42591</v>
       </c>
       <c r="C21" t="n">
@@ -9831,10 +9843,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C22" t="n">
@@ -9868,10 +9880,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="C23" t="n">
@@ -9905,10 +9917,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="C24" t="n">
@@ -9942,10 +9954,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="C25" t="n">
@@ -9979,10 +9991,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C26" t="n">
@@ -10016,10 +10028,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C27" t="n">
@@ -10053,10 +10065,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C28" t="n">
@@ -10090,10 +10102,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="C29" t="n">
@@ -10127,10 +10139,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C30" t="n">
@@ -10164,10 +10176,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C31" t="n">
@@ -10201,10 +10213,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C32" t="n">
@@ -10238,10 +10250,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="C33" t="n">
@@ -10275,10 +10287,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="C34" t="n">
@@ -10312,10 +10324,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C35" t="n">
@@ -10349,10 +10361,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C36" t="n">
@@ -10386,10 +10398,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="C37" t="n">
@@ -10423,10 +10435,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C38" t="n">
@@ -10460,10 +10472,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C39" t="n">
@@ -10497,10 +10509,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C40" t="n">
@@ -10534,10 +10546,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="C41" t="n">
@@ -10571,10 +10583,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C42" t="n">
@@ -10608,10 +10620,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C43" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C44" t="n">
@@ -10682,10 +10694,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="C45" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C46" t="n">
@@ -10756,10 +10768,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C47" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C48" t="n">
@@ -10830,10 +10842,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="C49" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C50" t="n">
@@ -10904,10 +10916,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="C51" t="n">
@@ -10941,10 +10953,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="C52" t="n">
@@ -10978,10 +10990,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="C53" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="C54" t="n">
@@ -11052,10 +11064,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="C55" t="n">
@@ -11089,10 +11101,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C56" t="n">
@@ -11126,10 +11138,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C57" t="n">
@@ -11163,10 +11175,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="C58" t="n">
@@ -11200,10 +11212,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="C59" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C60" t="n">
@@ -11274,10 +11286,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C61" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="C62" t="n">
@@ -11348,10 +11360,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="C63" t="n">
@@ -11403,12 +11415,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
